--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.3634694643809</v>
+        <v>8.184063787961897</v>
       </c>
       <c r="D2" t="n">
-        <v>37.53142060281965</v>
+        <v>6.098855847958194</v>
       </c>
       <c r="E2" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F2" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.02818952559245</v>
+        <v>3.092080797908773</v>
       </c>
       <c r="D3" t="n">
-        <v>11.62128069763676</v>
+        <v>1.888458113365973</v>
       </c>
       <c r="E3" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F3" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.79600922678012</v>
+        <v>5.166851499351769</v>
       </c>
       <c r="D4" t="n">
-        <v>19.91230775173988</v>
+        <v>3.23575000965773</v>
       </c>
       <c r="E4" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F4" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.386788170198</v>
+        <v>9.325353077657176</v>
       </c>
       <c r="D5" t="n">
-        <v>44.61081937491713</v>
+        <v>7.249258148424035</v>
       </c>
       <c r="E5" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F5" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.0359951573794</v>
+        <v>7.318349213074153</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0465950028863</v>
+        <v>1.632571687969024</v>
       </c>
       <c r="E6" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F6" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.89253002217032</v>
+        <v>10.38253612860268</v>
       </c>
       <c r="D7" t="n">
-        <v>48.1043323582476</v>
+        <v>7.816954008215236</v>
       </c>
       <c r="E7" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F7" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>60.19295979121159</v>
+        <v>9.781355966071883</v>
       </c>
       <c r="D8" t="n">
-        <v>16.92348301777779</v>
+        <v>2.750065990388892</v>
       </c>
       <c r="E8" t="n">
-        <v>15.09876034259884</v>
+        <v>2.453548555672311</v>
       </c>
       <c r="F8" t="n">
-        <v>14.84265203493405</v>
+        <v>2.411930955676784</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
